--- a/past/2025/2007-2024_ Hesap-Toplamlar/010_ 2016-23 BANKA/TL_AUB58001268616_09.01.2018-02.01.2024.xlsx
+++ b/past/2025/2007-2024_ Hesap-Toplamlar/010_ 2016-23 BANKA/TL_AUB58001268616_09.01.2018-02.01.2024.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\tdy\2007-2023_ Hesap-Toplamlar\010_ 2016-23 BANKA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\past\2025\2007-2024_ Hesap-Toplamlar\010_ 2016-23 BANKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C75D257F-8C14-4E07-90E3-A7FB5A22CF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A69A95C7-F5EC-412D-B093-B7D63B7700DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="750" windowWidth="16065" windowHeight="14835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="319927853_20240123_HesapÖzeti" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4229" uniqueCount="2254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4233" uniqueCount="2255">
   <si>
     <t>Büyük Mükellefler V. D. Başkanlığı</t>
   </si>
@@ -6794,6 +6794,9 @@
   </si>
   <si>
     <t>aylık giden ortalama nakit</t>
+  </si>
+  <si>
+    <t>ALİ UMUT BALCI</t>
   </si>
 </sst>
 </file>
@@ -7314,7 +7317,8 @@
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="7" width="12.42578125" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
@@ -7336,6 +7340,27 @@
         <v>1</v>
       </c>
     </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C3" s="2" t="s">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="C5" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="5">
+        <v>10000</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
     <row r="6" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="J6" s="1" t="s">
         <v>2</v>
